--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_14/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_14/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>63.93</v>
+        <v>64.91</v>
       </c>
       <c r="D2" t="n">
-        <v>18.44</v>
+        <v>17.37</v>
       </c>
       <c r="E2" t="n">
-        <v>28.85</v>
+        <v>26.75</v>
       </c>
       <c r="F2" t="n">
-        <v>42.4</v>
+        <v>44.49</v>
       </c>
       <c r="G2" t="n">
-        <v>47.2</v>
+        <v>49.26</v>
       </c>
       <c r="H2" t="n">
-        <v>59.5</v>
+        <v>62.83</v>
       </c>
       <c r="I2" t="n">
-        <v>79.01000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>57.6</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>47.15</v>
+        <v>45.38</v>
       </c>
       <c r="D3" t="n">
-        <v>1.14</v>
+        <v>0.6</v>
       </c>
       <c r="E3" t="n">
-        <v>2.41</v>
+        <v>1.33</v>
       </c>
       <c r="F3" t="n">
-        <v>43.26</v>
+        <v>43.01</v>
       </c>
       <c r="G3" t="n">
-        <v>47.08</v>
+        <v>45.5</v>
       </c>
       <c r="H3" t="n">
-        <v>47.64</v>
+        <v>45.5</v>
       </c>
       <c r="I3" t="n">
-        <v>47.72</v>
+        <v>45.52</v>
       </c>
       <c r="J3" t="n">
-        <v>48.23</v>
+        <v>45.69</v>
       </c>
       <c r="K3" t="n">
-        <v>4.97</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>7.77</v>
+        <v>9.51</v>
       </c>
       <c r="D4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="E4" t="n">
-        <v>17.38</v>
+        <v>14.62</v>
       </c>
       <c r="F4" t="n">
-        <v>5.54</v>
+        <v>6.25</v>
       </c>
       <c r="G4" t="n">
-        <v>6.74</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>7.24</v>
+        <v>9.91</v>
       </c>
       <c r="I4" t="n">
-        <v>8.869999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="J4" t="n">
-        <v>10.18</v>
+        <v>10.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>109.94</v>
+        <v>122.09</v>
       </c>
       <c r="D5" t="n">
-        <v>9.789999999999999</v>
+        <v>11.35</v>
       </c>
       <c r="E5" t="n">
-        <v>8.9</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>83.98999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="G5" t="n">
-        <v>101.49</v>
+        <v>119.74</v>
       </c>
       <c r="H5" t="n">
-        <v>114.74</v>
+        <v>124.01</v>
       </c>
       <c r="I5" t="n">
-        <v>117.45</v>
+        <v>126.07</v>
       </c>
       <c r="J5" t="n">
-        <v>121.44</v>
+        <v>148.79</v>
       </c>
       <c r="K5" t="n">
-        <v>37.44</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>3.08</v>
+        <v>4.73</v>
       </c>
       <c r="D6" t="n">
-        <v>0.86</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>27.85</v>
+        <v>4.34</v>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>4.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>4.72</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>4.91</v>
       </c>
       <c r="J6" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.81</v>
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
